--- a/data/processed/Neutralization.xlsx
+++ b/data/processed/Neutralization.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e4de212fc1e0fe75/Escritorio/Analisis vacuna BVDV/Manuscrito-BVDV-challenge/data/processed/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F558EF29-F518-4308-BA3C-D3B9EBE8890D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{F558EF29-F518-4308-BA3C-D3B9EBE8890D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{69CC26E9-9220-4071-971B-D8C9CFE257D1}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E99C7201-F25D-4421-96D2-AC6AA2A6A2C2}"/>
   </bookViews>
@@ -477,7 +477,7 @@
         <v>8</v>
       </c>
       <c r="D2">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -491,7 +491,7 @@
         <v>8</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -799,7 +799,7 @@
         <v>9</v>
       </c>
       <c r="D25">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -813,7 +813,7 @@
         <v>9</v>
       </c>
       <c r="D26">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
@@ -1121,7 +1121,7 @@
         <v>10</v>
       </c>
       <c r="D48">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
@@ -1135,7 +1135,7 @@
         <v>10</v>
       </c>
       <c r="D49">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
@@ -1443,7 +1443,7 @@
         <v>11</v>
       </c>
       <c r="D71">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
@@ -1457,7 +1457,7 @@
         <v>11</v>
       </c>
       <c r="D72">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
